--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487085_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487085_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8144</v>
+        <v>5.4888</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1564</v>
+        <v>5.8748</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6579</v>
+        <v>-0.3861</v>
       </c>
       <c r="G2" t="n">
         <v>-1.3559</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7879</v>
+        <v>0.4623</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4574</v>
+        <v>0.1759</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3305</v>
+        <v>0.2865</v>
       </c>
       <c r="V2" t="n">
         <v>5.6103</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8195</v>
+        <v>3.6732</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9222</v>
+        <v>5.642</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1027</v>
+        <v>-1.9688</v>
       </c>
       <c r="G3" t="n">
         <v>-2.1988</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8309</v>
+        <v>0.0228</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7733</v>
+        <v>-0.0535</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0575</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>3.7261</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0842</v>
+        <v>0.1825</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0172</v>
+        <v>0.1768</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1014</v>
+        <v>0.0057</v>
       </c>
       <c r="G4" t="n">
         <v>0.7297</v>
@@ -766,13 +766,13 @@
         <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1071</v>
+        <v>0.1596</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0449</v>
+        <v>0.1147</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0621</v>
+        <v>0.0449</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8999</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1435</v>
+        <v>-0.0433</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6224</v>
+        <v>-0.5222</v>
       </c>
       <c r="F5" t="n">
         <v>0.4789</v>
@@ -844,10 +844,10 @@
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2961</v>
+        <v>-0.196</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1772</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3494</v>
+        <v>-0.7892</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3854</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.964</v>
+        <v>-0.7231</v>
       </c>
       <c r="G6" t="n">
         <v>0.8653999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2195</v>
+        <v>-0.6594</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7588</v>
+        <v>-0.4395</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4607</v>
+        <v>-0.2198</v>
       </c>
       <c r="V6" t="n">
         <v>1.5138</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.507</v>
+        <v>-1.161</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001</v>
+        <v>0.3202</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.508</v>
+        <v>-1.4812</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8759</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0178</v>
+        <v>0.3639</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1639</v>
+        <v>0.1553</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1818</v>
+        <v>0.2085</v>
       </c>
       <c r="V7" t="n">
         <v>-1.228</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4228</v>
+        <v>-2.2493</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9765</v>
+        <v>0.9358</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3993</v>
+        <v>-3.1851</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4529</v>
@@ -1078,13 +1078,13 @@
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1097</v>
+        <v>0.0638</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5024</v>
+        <v>0.4617</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6121</v>
+        <v>-0.3979</v>
       </c>
       <c r="V8" t="n">
         <v>1.228</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.195</v>
+        <v>-6.5385</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4476</v>
+        <v>-2.8714</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7474</v>
+        <v>-3.6671</v>
       </c>
       <c r="G9" t="n">
         <v>-4.385</v>
@@ -1156,13 +1156,13 @@
         <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4133</v>
+        <v>1.0698</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5197</v>
+        <v>1.0959</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1065</v>
+        <v>-0.0262</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3281</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.3406</v>
+        <v>-7.7259</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1675</v>
+        <v>-4.767</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1731</v>
+        <v>-2.9589</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6466</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1343</v>
+        <v>-0.5195</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4759</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6584</v>
+        <v>-0.4442</v>
       </c>
       <c r="V10" t="n">
         <v>0.3704</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.0575</v>
+        <v>-9.411</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7851</v>
+        <v>-6.1655</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2723</v>
+        <v>-3.2456</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8089</v>
@@ -1312,13 +1312,13 @@
         <v>1.5441</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1098</v>
+        <v>-0.4634</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7139</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.396</v>
+        <v>-0.3692</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8576</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.4661</v>
+        <v>-18.5737</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3347</v>
+        <v>-1.4426</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.1314</v>
+        <v>-17.1313</v>
       </c>
       <c r="G12" t="n">
         <v>-19.3466</v>
@@ -1390,13 +1390,13 @@
         <v>12.5456</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5884</v>
+        <v>0.3039000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4298000000000002</v>
+        <v>1.3222</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0182</v>
+        <v>-1.0183</v>
       </c>
       <c r="V12" t="n">
         <v>10.1193</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.220000000000001</v>
+        <v>7.5771</v>
       </c>
       <c r="E13" t="n">
-        <v>8.8789</v>
+        <v>7.4769</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3412</v>
+        <v>0.1002</v>
       </c>
       <c r="G13" t="n">
         <v>3.6585</v>
@@ -1468,13 +1468,13 @@
         <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4807</v>
+        <v>0.8378</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7926</v>
+        <v>0.3907</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6881</v>
+        <v>0.4471</v>
       </c>
       <c r="V13" t="n">
         <v>0.5717</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1904</v>
+        <v>5.5571</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3831</v>
+        <v>4.1234</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8073</v>
+        <v>1.4336</v>
       </c>
       <c r="G14" t="n">
-        <v>3.564</v>
+        <v>3.9429</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7308</v>
+        <v>-0.5568</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2948</v>
+        <v>4.4998</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1985</v>
+        <v>4.203</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6983</v>
+        <v>-0.1761</v>
       </c>
       <c r="L14" t="n">
-        <v>3.5001</v>
+        <v>4.3791</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6345</v>
+        <v>-0.2601</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4292</v>
+        <v>-0.3808</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7947</v>
+        <v>0.1207</v>
       </c>
       <c r="P14" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.0532</v>
+        <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7386</v>
+        <v>0.2631</v>
       </c>
       <c r="T14" t="n">
-        <v>3.736</v>
+        <v>-0.0796</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0026</v>
+        <v>0.3427</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2702</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0831</v>
+        <v>5.3741</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6227</v>
+        <v>3.7852</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4604</v>
+        <v>1.589</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9429</v>
+        <v>2.8813</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5568</v>
+        <v>-1.6591</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4998</v>
+        <v>4.5405</v>
       </c>
       <c r="J15" t="n">
-        <v>4.203</v>
+        <v>3.7694</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1761</v>
+        <v>-0.2434</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3791</v>
+        <v>4.0128</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2601</v>
+        <v>-0.8881</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3808</v>
+        <v>-1.4157</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1207</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3511</v>
+        <v>2.8951</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>2.8951</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2109</v>
+        <v>0.0103</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5803</v>
+        <v>0.1425</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3695</v>
+        <v>-0.1322</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.4126</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6066</v>
+        <v>4.9136</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8729</v>
+        <v>4.0731</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7337</v>
+        <v>0.8405</v>
       </c>
       <c r="G16" t="n">
         <v>3.1603</v>
@@ -1702,13 +1702,13 @@
         <v>3.6672</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6418</v>
+        <v>-0.3348</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2697</v>
+        <v>-0.0694</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3722</v>
+        <v>-0.2654</v>
       </c>
       <c r="V16" t="n">
         <v>-0.614</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3658</v>
+        <v>4.4192</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8839</v>
+        <v>1.8796</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4819</v>
+        <v>2.5396</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8813</v>
+        <v>3.564</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6591</v>
+        <v>-0.7308</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5405</v>
+        <v>4.2948</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7694</v>
+        <v>4.1985</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2434</v>
+        <v>0.6983</v>
       </c>
       <c r="L17" t="n">
-        <v>4.0128</v>
+        <v>3.5001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8881</v>
+        <v>-0.6345</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4157</v>
+        <v>-1.4292</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.7947</v>
       </c>
       <c r="P17" t="n">
-        <v>2.8951</v>
+        <v>1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8951</v>
+        <v>4.0532</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9981</v>
+        <v>0.9674</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7588</v>
+        <v>1.2325</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2393</v>
+        <v>-0.2651</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4126</v>
+        <v>-1.2702</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1267</v>
+        <v>-0.6562</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0428</v>
+        <v>4.0112</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8171</v>
+        <v>2.5181</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2257</v>
+        <v>1.4931</v>
       </c>
       <c r="G18" t="n">
         <v>1.1264</v>
@@ -1858,13 +1858,13 @@
         <v>2.7021</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1138</v>
+        <v>-0.1454</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8183</v>
+        <v>-0.1173</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2955</v>
+        <v>-0.0281</v>
       </c>
       <c r="V18" t="n">
         <v>0.3281</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0594</v>
+        <v>2.0326</v>
       </c>
       <c r="E19" t="n">
         <v>2.5805</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5211</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>2.9525</v>
@@ -1936,13 +1936,13 @@
         <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2346</v>
+        <v>0.2079</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0449</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2796</v>
+        <v>0.2528</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5138</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9328</v>
+        <v>-1.7725</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7752</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1576</v>
+        <v>-0.9973</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4875</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1752</v>
+        <v>-0.0149</v>
       </c>
       <c r="T20" t="n">
         <v>-0.119</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0562</v>
+        <v>0.1041</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2702</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5984</v>
+        <v>-1.9518</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1432</v>
+        <v>-1.7368</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4552</v>
+        <v>-0.215</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7472</v>
+        <v>-0.7406</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7472</v>
+        <v>0.3375</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-1.0782</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0207</v>
+        <v>0.5749</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0207</v>
+        <v>1.7801</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.2052</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7679</v>
+        <v>-1.3155</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7679</v>
+        <v>-1.4426</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.1271</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>-0.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2023</v>
+        <v>-0.3041</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1639</v>
+        <v>-0.0535</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0383</v>
+        <v>-0.2505</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.842</v>
+        <v>-0.3281</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6326</v>
+        <v>-2.3112</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3377</v>
+        <v>-0.0431</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2949</v>
+        <v>-2.2681</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7406</v>
+        <v>-0.7472</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3375</v>
+        <v>-0.7472</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0782</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5749</v>
+        <v>0.0207</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7801</v>
+        <v>0.0207</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2052</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3155</v>
+        <v>-0.7679</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4426</v>
+        <v>-0.7679</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1271</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.579</v>
+        <v>0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9849</v>
+        <v>0.0849</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6544</v>
+        <v>-0.0638</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3305</v>
+        <v>0.1487</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3281</v>
+        <v>-1.842</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.328</v>
+        <v>-3.8402</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7217</v>
+        <v>-2.4213</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6062</v>
+        <v>-1.4188</v>
       </c>
       <c r="G23" t="n">
         <v>0.0433</v>
@@ -2248,13 +2248,13 @@
         <v>0.772</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6921</v>
+        <v>-0.2042</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3424</v>
+        <v>-0.042</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3497</v>
+        <v>-0.1623</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5561</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6102</v>
+        <v>-3.8755</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9299</v>
+        <v>-4.3291</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3197</v>
+        <v>0.4535</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0071</v>
@@ -2326,13 +2326,13 @@
         <v>2.3161</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8467</v>
+        <v>-0.112</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7588</v>
+        <v>-0.158</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.0459</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2123</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>19.4661</v>
+        <v>20.1337</v>
       </c>
       <c r="E25" t="n">
-        <v>17.1314</v>
+        <v>17.1313</v>
       </c>
       <c r="F25" t="n">
-        <v>2.3349</v>
+        <v>3.002400000000001</v>
       </c>
       <c r="G25" t="n">
         <v>19.3468</v>
@@ -2377,7 +2377,7 @@
         <v>18.3789</v>
       </c>
       <c r="J25" t="n">
-        <v>27.52500000000001</v>
+        <v>27.525</v>
       </c>
       <c r="K25" t="n">
         <v>11.0524</v>
@@ -2404,13 +2404,13 @@
         <v>22.196</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5881000000000001</v>
+        <v>1.256</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0181</v>
+        <v>1.0182</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4297999999999997</v>
+        <v>0.2377</v>
       </c>
       <c r="V25" t="n">
         <v>-10.1195</v>
